--- a/KOSMETICOS ETL SOFTWARE/Base_de_datos/Excel_Main_10_Productos.xlsx
+++ b/KOSMETICOS ETL SOFTWARE/Base_de_datos/Excel_Main_10_Productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\opera\OneDrive\Escritorio\KOSMETICOS ETL SOFTWARE(1)\KOSMETICOS ETL SOFTWARE\Base_de_datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA99E7DB-2808-4EC9-8C30-AD96FBEF7163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2FDF20B-04EF-48CD-9939-DE3DD3DC7A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="195">
   <si>
     <t>SKU_Padre</t>
   </si>
@@ -668,6 +668,18 @@
   </si>
   <si>
     <t>SI</t>
+  </si>
+  <si>
+    <t>BOJ001901</t>
+  </si>
+  <si>
+    <t>Ginseng Holiday Kit</t>
+  </si>
+  <si>
+    <t>kit</t>
+  </si>
+  <si>
+    <t>SKINCARE / KIT</t>
   </si>
 </sst>
 </file>
@@ -742,7 +754,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -750,8 +762,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1055,7 +1070,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD18"/>
+  <dimension ref="A1:AD19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="30" width="30" customWidth="1"/>
@@ -2353,6 +2368,44 @@
         <v>178</v>
       </c>
     </row>
+    <row r="19" spans="1:30" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:AD17" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
